--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3759,6 +3759,1561 @@
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128721535</v>
+      </c>
+      <c r="B32" t="n">
+        <v>75115</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gyle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>715312</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6368398</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128721573</v>
+      </c>
+      <c r="B33" t="n">
+        <v>86890</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Gyle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>715594</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6368467</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128721633</v>
+      </c>
+      <c r="B34" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Gyle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>715511</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6368537</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128721515</v>
+      </c>
+      <c r="B35" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Gyle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>715687</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6368449</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128721555</v>
+      </c>
+      <c r="B36" t="n">
+        <v>86949</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>449</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Gyle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>715312</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6368391</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128721565</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98590</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Gyle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>715699</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6368412</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128721574</v>
+      </c>
+      <c r="B38" t="n">
+        <v>86890</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Gyle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>715274</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6368569</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128721630</v>
+      </c>
+      <c r="B39" t="n">
+        <v>86927</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Gyle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>715736</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6368332</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128721561</v>
+      </c>
+      <c r="B40" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Gyle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>715317</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6368305</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128721532</v>
+      </c>
+      <c r="B41" t="n">
+        <v>75115</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Gyle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>715763</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6368338</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128721498</v>
+      </c>
+      <c r="B42" t="n">
+        <v>86972</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>3767</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Violettfläckig spindling</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Gyle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>715536</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6368516</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128721536</v>
+      </c>
+      <c r="B43" t="n">
+        <v>75115</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Gyle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>715317</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6368307</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128721566</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98590</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Gyle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>715339</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6368362</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128721556</v>
+      </c>
+      <c r="B45" t="n">
+        <v>86949</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>449</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Gyle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>715325</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6368299</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128721551</v>
+      </c>
+      <c r="B46" t="n">
+        <v>86843</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Gyle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>715379</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6368253</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128721533</v>
+      </c>
+      <c r="B47" t="n">
+        <v>75115</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Gyle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>715262</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6368453</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -3851,7 +3851,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4241,17 +4241,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128721565</v>
+        <v>128721574</v>
       </c>
       <c r="B37" t="n">
-        <v>98590</v>
+        <v>86890</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4259,21 +4259,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219811</v>
+        <v>3674</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715699</v>
+        <v>715274</v>
       </c>
       <c r="R37" t="n">
-        <v>6368412</v>
+        <v>6368569</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4338,17 +4338,17 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128721574</v>
+        <v>128721565</v>
       </c>
       <c r="B38" t="n">
-        <v>86890</v>
+        <v>98590</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4356,21 +4356,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3674</v>
+        <v>219811</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715274</v>
+        <v>715699</v>
       </c>
       <c r="R38" t="n">
-        <v>6368569</v>
+        <v>6368412</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -3851,39 +3851,39 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128721573</v>
+        <v>128721633</v>
       </c>
       <c r="B33" t="n">
-        <v>86890</v>
+        <v>86927</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>715594</v>
+        <v>715511</v>
       </c>
       <c r="R33" t="n">
-        <v>6368467</v>
+        <v>6368537</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3937,50 +3937,51 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128721633</v>
+        <v>128721573</v>
       </c>
       <c r="B34" t="n">
-        <v>86927</v>
+        <v>86890</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3990,10 +3991,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>715511</v>
+        <v>715594</v>
       </c>
       <c r="R34" t="n">
-        <v>6368537</v>
+        <v>6368467</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4034,19 +4035,18 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4348,7 +4348,7 @@
         <v>128721565</v>
       </c>
       <c r="B38" t="n">
-        <v>98590</v>
+        <v>98593</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4435,39 +4435,39 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128721630</v>
+        <v>128721561</v>
       </c>
       <c r="B39" t="n">
-        <v>86927</v>
+        <v>4779</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6003295</v>
+        <v>102306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>715736</v>
+        <v>715317</v>
       </c>
       <c r="R39" t="n">
-        <v>6368332</v>
+        <v>6368305</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4521,51 +4521,50 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128721561</v>
+        <v>128721630</v>
       </c>
       <c r="B40" t="n">
-        <v>4779</v>
+        <v>86927</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102306</v>
+        <v>6003295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4575,10 +4574,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>715317</v>
+        <v>715736</v>
       </c>
       <c r="R40" t="n">
-        <v>6368305</v>
+        <v>6368332</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4619,18 +4618,19 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -4931,7 +4931,7 @@
         <v>128721566</v>
       </c>
       <c r="B44" t="n">
-        <v>98590</v>
+        <v>98593</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -4151,32 +4151,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128721555</v>
+        <v>128721565</v>
       </c>
       <c r="B36" t="n">
-        <v>86949</v>
+        <v>98593</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>449</v>
+        <v>219811</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4186,10 +4186,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>715312</v>
+        <v>715699</v>
       </c>
       <c r="R36" t="n">
-        <v>6368391</v>
+        <v>6368412</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4248,32 +4248,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128721574</v>
+        <v>128721555</v>
       </c>
       <c r="B37" t="n">
-        <v>86890</v>
+        <v>86949</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715274</v>
+        <v>715312</v>
       </c>
       <c r="R37" t="n">
-        <v>6368569</v>
+        <v>6368391</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4345,10 +4345,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128721565</v>
+        <v>128721574</v>
       </c>
       <c r="B38" t="n">
-        <v>98593</v>
+        <v>86890</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4356,21 +4356,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219811</v>
+        <v>3674</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715699</v>
+        <v>715274</v>
       </c>
       <c r="R38" t="n">
-        <v>6368412</v>
+        <v>6368569</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -4151,32 +4151,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128721565</v>
+        <v>128721555</v>
       </c>
       <c r="B36" t="n">
-        <v>98593</v>
+        <v>86949</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219811</v>
+        <v>449</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4186,10 +4186,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>715699</v>
+        <v>715312</v>
       </c>
       <c r="R36" t="n">
-        <v>6368412</v>
+        <v>6368391</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4248,32 +4248,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128721555</v>
+        <v>128721574</v>
       </c>
       <c r="B37" t="n">
-        <v>86949</v>
+        <v>86890</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715312</v>
+        <v>715274</v>
       </c>
       <c r="R37" t="n">
-        <v>6368391</v>
+        <v>6368569</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4345,10 +4345,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128721574</v>
+        <v>128721565</v>
       </c>
       <c r="B38" t="n">
-        <v>86890</v>
+        <v>98594</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4356,21 +4356,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3674</v>
+        <v>219811</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715274</v>
+        <v>715699</v>
       </c>
       <c r="R38" t="n">
-        <v>6368569</v>
+        <v>6368412</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4931,7 +4931,7 @@
         <v>128721566</v>
       </c>
       <c r="B44" t="n">
-        <v>98593</v>
+        <v>98594</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5122,32 +5122,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128721551</v>
+        <v>128721533</v>
       </c>
       <c r="B46" t="n">
-        <v>86843</v>
+        <v>75115</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>248956</v>
+        <v>6426</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5157,10 +5157,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>715379</v>
+        <v>715262</v>
       </c>
       <c r="R46" t="n">
-        <v>6368253</v>
+        <v>6368453</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5219,32 +5219,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128721533</v>
+        <v>128721551</v>
       </c>
       <c r="B47" t="n">
-        <v>75115</v>
+        <v>86843</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6426</v>
+        <v>248956</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5254,10 +5254,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>715262</v>
+        <v>715379</v>
       </c>
       <c r="R47" t="n">
-        <v>6368453</v>
+        <v>6368253</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -3764,7 +3764,7 @@
         <v>128721535</v>
       </c>
       <c r="B32" t="n">
-        <v>75115</v>
+        <v>75142</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3861,7 +3861,7 @@
         <v>128721633</v>
       </c>
       <c r="B33" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>128721573</v>
       </c>
       <c r="B34" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4056,7 +4056,7 @@
         <v>128721515</v>
       </c>
       <c r="B35" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4154,7 +4154,7 @@
         <v>128721555</v>
       </c>
       <c r="B36" t="n">
-        <v>86949</v>
+        <v>86976</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4251,7 +4251,7 @@
         <v>128721574</v>
       </c>
       <c r="B37" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4348,7 +4348,7 @@
         <v>128721565</v>
       </c>
       <c r="B38" t="n">
-        <v>98594</v>
+        <v>98621</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4542,7 +4542,7 @@
         <v>128721630</v>
       </c>
       <c r="B40" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>128721532</v>
       </c>
       <c r="B41" t="n">
-        <v>75115</v>
+        <v>75142</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4737,7 +4737,7 @@
         <v>128721498</v>
       </c>
       <c r="B42" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4834,7 +4834,7 @@
         <v>128721536</v>
       </c>
       <c r="B43" t="n">
-        <v>75115</v>
+        <v>75142</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -4931,7 +4931,7 @@
         <v>128721566</v>
       </c>
       <c r="B44" t="n">
-        <v>98594</v>
+        <v>98621</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5028,7 +5028,7 @@
         <v>128721556</v>
       </c>
       <c r="B45" t="n">
-        <v>86949</v>
+        <v>86976</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5125,7 +5125,7 @@
         <v>128721533</v>
       </c>
       <c r="B46" t="n">
-        <v>75115</v>
+        <v>75142</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5222,7 +5222,7 @@
         <v>128721551</v>
       </c>
       <c r="B47" t="n">
-        <v>86843</v>
+        <v>86870</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -3851,7 +3851,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4144,39 +4144,39 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128721555</v>
+        <v>128721574</v>
       </c>
       <c r="B36" t="n">
-        <v>86976</v>
+        <v>86917</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4186,10 +4186,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>715312</v>
+        <v>715274</v>
       </c>
       <c r="R36" t="n">
-        <v>6368391</v>
+        <v>6368569</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4241,17 +4241,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128721574</v>
+        <v>128721565</v>
       </c>
       <c r="B37" t="n">
-        <v>86917</v>
+        <v>98621</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4259,21 +4259,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3674</v>
+        <v>219811</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715274</v>
+        <v>715699</v>
       </c>
       <c r="R37" t="n">
-        <v>6368569</v>
+        <v>6368412</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4338,39 +4338,39 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128721565</v>
+        <v>128721555</v>
       </c>
       <c r="B38" t="n">
-        <v>98621</v>
+        <v>86976</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219811</v>
+        <v>449</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715699</v>
+        <v>715312</v>
       </c>
       <c r="R38" t="n">
-        <v>6368412</v>
+        <v>6368391</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -3764,7 +3764,7 @@
         <v>128721535</v>
       </c>
       <c r="B32" t="n">
-        <v>75142</v>
+        <v>75143</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3858,32 +3858,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128721633</v>
+        <v>128721573</v>
       </c>
       <c r="B33" t="n">
-        <v>86954</v>
+        <v>86921</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>715511</v>
+        <v>715594</v>
       </c>
       <c r="R33" t="n">
-        <v>6368537</v>
+        <v>6368467</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3937,51 +3937,50 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128721573</v>
+        <v>128721633</v>
       </c>
       <c r="B34" t="n">
-        <v>86917</v>
+        <v>86958</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3991,10 +3990,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>715594</v>
+        <v>715511</v>
       </c>
       <c r="R34" t="n">
-        <v>6368467</v>
+        <v>6368537</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4035,18 +4034,19 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4056,7 +4056,7 @@
         <v>128721515</v>
       </c>
       <c r="B35" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4151,32 +4151,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128721574</v>
+        <v>128721555</v>
       </c>
       <c r="B36" t="n">
-        <v>86917</v>
+        <v>86980</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4186,10 +4186,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>715274</v>
+        <v>715312</v>
       </c>
       <c r="R36" t="n">
-        <v>6368569</v>
+        <v>6368391</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4248,10 +4248,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128721565</v>
+        <v>128721574</v>
       </c>
       <c r="B37" t="n">
-        <v>98621</v>
+        <v>86921</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4259,21 +4259,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219811</v>
+        <v>3674</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715699</v>
+        <v>715274</v>
       </c>
       <c r="R37" t="n">
-        <v>6368412</v>
+        <v>6368569</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4345,32 +4345,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128721555</v>
+        <v>128721565</v>
       </c>
       <c r="B38" t="n">
-        <v>86976</v>
+        <v>98627</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>449</v>
+        <v>219811</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715312</v>
+        <v>715699</v>
       </c>
       <c r="R38" t="n">
-        <v>6368391</v>
+        <v>6368412</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4542,7 +4542,7 @@
         <v>128721630</v>
       </c>
       <c r="B40" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>128721532</v>
       </c>
       <c r="B41" t="n">
-        <v>75142</v>
+        <v>75143</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>128721498</v>
       </c>
       <c r="B42" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>128721536</v>
       </c>
       <c r="B43" t="n">
-        <v>75142</v>
+        <v>75143</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>128721566</v>
       </c>
       <c r="B44" t="n">
-        <v>98621</v>
+        <v>98627</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>128721556</v>
       </c>
       <c r="B45" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>128721533</v>
       </c>
       <c r="B46" t="n">
-        <v>75142</v>
+        <v>75143</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>128721551</v>
       </c>
       <c r="B47" t="n">
-        <v>86870</v>
+        <v>86874</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -3861,7 +3861,7 @@
         <v>128721573</v>
       </c>
       <c r="B33" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>128721633</v>
       </c>
       <c r="B34" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>128721515</v>
       </c>
       <c r="B35" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4151,32 +4151,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128721555</v>
+        <v>128721565</v>
       </c>
       <c r="B36" t="n">
-        <v>86980</v>
+        <v>98634</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>449</v>
+        <v>219811</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4186,10 +4186,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>715312</v>
+        <v>715699</v>
       </c>
       <c r="R36" t="n">
-        <v>6368391</v>
+        <v>6368412</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4248,32 +4248,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128721574</v>
+        <v>128721555</v>
       </c>
       <c r="B37" t="n">
-        <v>86921</v>
+        <v>86981</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715274</v>
+        <v>715312</v>
       </c>
       <c r="R37" t="n">
-        <v>6368569</v>
+        <v>6368391</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4345,10 +4345,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128721565</v>
+        <v>128721574</v>
       </c>
       <c r="B38" t="n">
-        <v>98627</v>
+        <v>86922</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4356,21 +4356,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219811</v>
+        <v>3674</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715699</v>
+        <v>715274</v>
       </c>
       <c r="R38" t="n">
-        <v>6368412</v>
+        <v>6368569</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4542,7 +4542,7 @@
         <v>128721630</v>
       </c>
       <c r="B40" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>128721498</v>
       </c>
       <c r="B42" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>128721566</v>
       </c>
       <c r="B44" t="n">
-        <v>98627</v>
+        <v>98634</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>128721556</v>
       </c>
       <c r="B45" t="n">
-        <v>86980</v>
+        <v>86981</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>128721551</v>
       </c>
       <c r="B47" t="n">
-        <v>86874</v>
+        <v>86875</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -3858,32 +3858,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128721573</v>
+        <v>128721633</v>
       </c>
       <c r="B33" t="n">
-        <v>86922</v>
+        <v>86959</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>715594</v>
+        <v>715511</v>
       </c>
       <c r="R33" t="n">
-        <v>6368467</v>
+        <v>6368537</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3937,50 +3937,51 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128721633</v>
+        <v>128721573</v>
       </c>
       <c r="B34" t="n">
-        <v>86959</v>
+        <v>86922</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3990,10 +3991,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>715511</v>
+        <v>715594</v>
       </c>
       <c r="R34" t="n">
-        <v>6368537</v>
+        <v>6368467</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4034,19 +4035,18 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4151,32 +4151,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128721565</v>
+        <v>128721555</v>
       </c>
       <c r="B36" t="n">
-        <v>98634</v>
+        <v>86981</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219811</v>
+        <v>449</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4186,10 +4186,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>715699</v>
+        <v>715312</v>
       </c>
       <c r="R36" t="n">
-        <v>6368412</v>
+        <v>6368391</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4248,32 +4248,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128721555</v>
+        <v>128721574</v>
       </c>
       <c r="B37" t="n">
-        <v>86981</v>
+        <v>86922</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715312</v>
+        <v>715274</v>
       </c>
       <c r="R37" t="n">
-        <v>6368391</v>
+        <v>6368569</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4345,10 +4345,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128721574</v>
+        <v>128721565</v>
       </c>
       <c r="B38" t="n">
-        <v>86922</v>
+        <v>98634</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4356,21 +4356,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3674</v>
+        <v>219811</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715274</v>
+        <v>715699</v>
       </c>
       <c r="R38" t="n">
-        <v>6368569</v>
+        <v>6368412</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -3764,7 +3764,7 @@
         <v>128721535</v>
       </c>
       <c r="B32" t="n">
-        <v>75143</v>
+        <v>75147</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3858,32 +3858,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128721633</v>
+        <v>128721573</v>
       </c>
       <c r="B33" t="n">
-        <v>86959</v>
+        <v>86926</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>715511</v>
+        <v>715594</v>
       </c>
       <c r="R33" t="n">
-        <v>6368537</v>
+        <v>6368467</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3937,51 +3937,50 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128721573</v>
+        <v>128721633</v>
       </c>
       <c r="B34" t="n">
-        <v>86922</v>
+        <v>86963</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3991,10 +3990,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>715594</v>
+        <v>715511</v>
       </c>
       <c r="R34" t="n">
-        <v>6368467</v>
+        <v>6368537</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4035,18 +4034,19 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4056,7 +4056,7 @@
         <v>128721515</v>
       </c>
       <c r="B35" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4151,32 +4151,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128721555</v>
+        <v>128721574</v>
       </c>
       <c r="B36" t="n">
-        <v>86981</v>
+        <v>86926</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4186,10 +4186,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>715312</v>
+        <v>715274</v>
       </c>
       <c r="R36" t="n">
-        <v>6368391</v>
+        <v>6368569</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4248,32 +4248,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128721574</v>
+        <v>128721555</v>
       </c>
       <c r="B37" t="n">
-        <v>86922</v>
+        <v>86985</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715274</v>
+        <v>715312</v>
       </c>
       <c r="R37" t="n">
-        <v>6368569</v>
+        <v>6368391</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4348,7 +4348,7 @@
         <v>128721565</v>
       </c>
       <c r="B38" t="n">
-        <v>98634</v>
+        <v>98638</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4442,32 +4442,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128721561</v>
+        <v>128721630</v>
       </c>
       <c r="B39" t="n">
-        <v>4779</v>
+        <v>86963</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102306</v>
+        <v>6003295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>715317</v>
+        <v>715736</v>
       </c>
       <c r="R39" t="n">
-        <v>6368305</v>
+        <v>6368332</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4521,50 +4521,51 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128721630</v>
+        <v>128721561</v>
       </c>
       <c r="B40" t="n">
-        <v>86959</v>
+        <v>4779</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6003295</v>
+        <v>102306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4574,10 +4575,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>715736</v>
+        <v>715317</v>
       </c>
       <c r="R40" t="n">
-        <v>6368332</v>
+        <v>6368305</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4618,19 +4619,18 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4640,7 +4640,7 @@
         <v>128721532</v>
       </c>
       <c r="B41" t="n">
-        <v>75143</v>
+        <v>75147</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4734,32 +4734,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128721498</v>
+        <v>128721536</v>
       </c>
       <c r="B42" t="n">
-        <v>87004</v>
+        <v>75147</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3767</v>
+        <v>6426</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>715536</v>
+        <v>715317</v>
       </c>
       <c r="R42" t="n">
-        <v>6368516</v>
+        <v>6368307</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4831,32 +4831,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128721536</v>
+        <v>128721498</v>
       </c>
       <c r="B43" t="n">
-        <v>75143</v>
+        <v>87008</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6426</v>
+        <v>3767</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4866,10 +4866,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>715317</v>
+        <v>715536</v>
       </c>
       <c r="R43" t="n">
-        <v>6368307</v>
+        <v>6368516</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4931,7 +4931,7 @@
         <v>128721566</v>
       </c>
       <c r="B44" t="n">
-        <v>98634</v>
+        <v>98638</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>128721556</v>
       </c>
       <c r="B45" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>128721533</v>
       </c>
       <c r="B46" t="n">
-        <v>75143</v>
+        <v>75147</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>128721551</v>
       </c>
       <c r="B47" t="n">
-        <v>86875</v>
+        <v>86879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -4248,32 +4248,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128721555</v>
+        <v>128721565</v>
       </c>
       <c r="B37" t="n">
-        <v>86985</v>
+        <v>98638</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>449</v>
+        <v>219811</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715312</v>
+        <v>715699</v>
       </c>
       <c r="R37" t="n">
-        <v>6368391</v>
+        <v>6368412</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4345,32 +4345,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128721565</v>
+        <v>128721555</v>
       </c>
       <c r="B38" t="n">
-        <v>98638</v>
+        <v>86985</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219811</v>
+        <v>449</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715699</v>
+        <v>715312</v>
       </c>
       <c r="R38" t="n">
-        <v>6368412</v>
+        <v>6368391</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4442,32 +4442,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128721630</v>
+        <v>128721561</v>
       </c>
       <c r="B39" t="n">
-        <v>86963</v>
+        <v>4779</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6003295</v>
+        <v>102306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>715736</v>
+        <v>715317</v>
       </c>
       <c r="R39" t="n">
-        <v>6368332</v>
+        <v>6368305</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4521,51 +4521,50 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128721561</v>
+        <v>128721630</v>
       </c>
       <c r="B40" t="n">
-        <v>4779</v>
+        <v>86963</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102306</v>
+        <v>6003295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4575,10 +4574,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>715317</v>
+        <v>715736</v>
       </c>
       <c r="R40" t="n">
-        <v>6368305</v>
+        <v>6368332</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4619,18 +4618,19 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4734,32 +4734,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128721536</v>
+        <v>128721498</v>
       </c>
       <c r="B42" t="n">
-        <v>75147</v>
+        <v>87008</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6426</v>
+        <v>3767</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>715317</v>
+        <v>715536</v>
       </c>
       <c r="R42" t="n">
-        <v>6368307</v>
+        <v>6368516</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4831,32 +4831,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128721498</v>
+        <v>128721536</v>
       </c>
       <c r="B43" t="n">
-        <v>87008</v>
+        <v>75147</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3767</v>
+        <v>6426</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4866,10 +4866,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>715536</v>
+        <v>715317</v>
       </c>
       <c r="R43" t="n">
-        <v>6368516</v>
+        <v>6368307</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -4151,10 +4151,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128721574</v>
+        <v>128721565</v>
       </c>
       <c r="B36" t="n">
-        <v>86926</v>
+        <v>98638</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4162,21 +4162,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3674</v>
+        <v>219811</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4186,10 +4186,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>715274</v>
+        <v>715699</v>
       </c>
       <c r="R36" t="n">
-        <v>6368569</v>
+        <v>6368412</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4248,32 +4248,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128721565</v>
+        <v>128721555</v>
       </c>
       <c r="B37" t="n">
-        <v>98638</v>
+        <v>86985</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219811</v>
+        <v>449</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715699</v>
+        <v>715312</v>
       </c>
       <c r="R37" t="n">
-        <v>6368412</v>
+        <v>6368391</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4345,32 +4345,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128721555</v>
+        <v>128721574</v>
       </c>
       <c r="B38" t="n">
-        <v>86985</v>
+        <v>86926</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715312</v>
+        <v>715274</v>
       </c>
       <c r="R38" t="n">
-        <v>6368391</v>
+        <v>6368569</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4734,32 +4734,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128721498</v>
+        <v>128721536</v>
       </c>
       <c r="B42" t="n">
-        <v>87008</v>
+        <v>75147</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3767</v>
+        <v>6426</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>715536</v>
+        <v>715317</v>
       </c>
       <c r="R42" t="n">
-        <v>6368516</v>
+        <v>6368307</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4831,32 +4831,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128721536</v>
+        <v>128721498</v>
       </c>
       <c r="B43" t="n">
-        <v>75147</v>
+        <v>87008</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6426</v>
+        <v>3767</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4866,10 +4866,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>715317</v>
+        <v>715536</v>
       </c>
       <c r="R43" t="n">
-        <v>6368307</v>
+        <v>6368516</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -3764,7 +3764,7 @@
         <v>128721535</v>
       </c>
       <c r="B32" t="n">
-        <v>75147</v>
+        <v>75150</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>128721573</v>
       </c>
       <c r="B33" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>128721633</v>
       </c>
       <c r="B34" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>128721515</v>
       </c>
       <c r="B35" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4151,32 +4151,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128721565</v>
+        <v>128721555</v>
       </c>
       <c r="B36" t="n">
-        <v>98638</v>
+        <v>86990</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219811</v>
+        <v>449</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4186,10 +4186,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>715699</v>
+        <v>715312</v>
       </c>
       <c r="R36" t="n">
-        <v>6368412</v>
+        <v>6368391</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4248,32 +4248,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128721555</v>
+        <v>128721574</v>
       </c>
       <c r="B37" t="n">
-        <v>86985</v>
+        <v>86931</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715312</v>
+        <v>715274</v>
       </c>
       <c r="R37" t="n">
-        <v>6368391</v>
+        <v>6368569</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4345,10 +4345,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128721574</v>
+        <v>128721565</v>
       </c>
       <c r="B38" t="n">
-        <v>86926</v>
+        <v>98645</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4356,21 +4356,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3674</v>
+        <v>219811</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715274</v>
+        <v>715699</v>
       </c>
       <c r="R38" t="n">
-        <v>6368569</v>
+        <v>6368412</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4542,7 +4542,7 @@
         <v>128721630</v>
       </c>
       <c r="B40" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>128721532</v>
       </c>
       <c r="B41" t="n">
-        <v>75147</v>
+        <v>75150</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4734,32 +4734,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128721536</v>
+        <v>128721498</v>
       </c>
       <c r="B42" t="n">
-        <v>75147</v>
+        <v>87013</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6426</v>
+        <v>3767</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>715317</v>
+        <v>715536</v>
       </c>
       <c r="R42" t="n">
-        <v>6368307</v>
+        <v>6368516</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4831,32 +4831,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128721498</v>
+        <v>128721536</v>
       </c>
       <c r="B43" t="n">
-        <v>87008</v>
+        <v>75150</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3767</v>
+        <v>6426</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4866,10 +4866,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>715536</v>
+        <v>715317</v>
       </c>
       <c r="R43" t="n">
-        <v>6368516</v>
+        <v>6368307</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4931,7 +4931,7 @@
         <v>128721566</v>
       </c>
       <c r="B44" t="n">
-        <v>98638</v>
+        <v>98645</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>128721556</v>
       </c>
       <c r="B45" t="n">
-        <v>86985</v>
+        <v>86990</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>128721533</v>
       </c>
       <c r="B46" t="n">
-        <v>75147</v>
+        <v>75150</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>128721551</v>
       </c>
       <c r="B47" t="n">
-        <v>86879</v>
+        <v>86884</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -3858,32 +3858,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128721573</v>
+        <v>128721633</v>
       </c>
       <c r="B33" t="n">
-        <v>86938</v>
+        <v>86978</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>715594</v>
+        <v>715511</v>
       </c>
       <c r="R33" t="n">
-        <v>6368467</v>
+        <v>6368537</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3937,50 +3937,51 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128721633</v>
+        <v>128721573</v>
       </c>
       <c r="B34" t="n">
-        <v>86975</v>
+        <v>86941</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3990,10 +3991,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>715511</v>
+        <v>715594</v>
       </c>
       <c r="R34" t="n">
-        <v>6368537</v>
+        <v>6368467</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4034,19 +4035,18 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4056,7 +4056,7 @@
         <v>128721515</v>
       </c>
       <c r="B35" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4151,32 +4151,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128721574</v>
+        <v>128721555</v>
       </c>
       <c r="B36" t="n">
-        <v>86938</v>
+        <v>87000</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4186,10 +4186,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>715274</v>
+        <v>715312</v>
       </c>
       <c r="R36" t="n">
-        <v>6368569</v>
+        <v>6368391</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4248,10 +4248,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128721565</v>
+        <v>128721574</v>
       </c>
       <c r="B37" t="n">
-        <v>98653</v>
+        <v>86941</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4259,21 +4259,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219811</v>
+        <v>3674</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715699</v>
+        <v>715274</v>
       </c>
       <c r="R37" t="n">
-        <v>6368412</v>
+        <v>6368569</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4345,32 +4345,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128721555</v>
+        <v>128721565</v>
       </c>
       <c r="B38" t="n">
-        <v>86997</v>
+        <v>98658</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>449</v>
+        <v>219811</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715312</v>
+        <v>715699</v>
       </c>
       <c r="R38" t="n">
-        <v>6368391</v>
+        <v>6368412</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4542,7 +4542,7 @@
         <v>128721630</v>
       </c>
       <c r="B40" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>128721498</v>
       </c>
       <c r="B42" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>128721566</v>
       </c>
       <c r="B44" t="n">
-        <v>98653</v>
+        <v>98658</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>128721556</v>
       </c>
       <c r="B45" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>128721551</v>
       </c>
       <c r="B47" t="n">
-        <v>86891</v>
+        <v>86894</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -3858,32 +3858,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128721633</v>
+        <v>128721573</v>
       </c>
       <c r="B33" t="n">
-        <v>86978</v>
+        <v>86944</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>715511</v>
+        <v>715594</v>
       </c>
       <c r="R33" t="n">
-        <v>6368537</v>
+        <v>6368467</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3937,51 +3937,50 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128721573</v>
+        <v>128721633</v>
       </c>
       <c r="B34" t="n">
-        <v>86941</v>
+        <v>86981</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3991,10 +3990,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>715594</v>
+        <v>715511</v>
       </c>
       <c r="R34" t="n">
-        <v>6368467</v>
+        <v>6368537</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4035,18 +4034,19 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4056,7 +4056,7 @@
         <v>128721515</v>
       </c>
       <c r="B35" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>128721555</v>
       </c>
       <c r="B36" t="n">
-        <v>87000</v>
+        <v>87003</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>128721574</v>
       </c>
       <c r="B37" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>128721565</v>
       </c>
       <c r="B38" t="n">
-        <v>98658</v>
+        <v>98661</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4442,32 +4442,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128721561</v>
+        <v>128721630</v>
       </c>
       <c r="B39" t="n">
-        <v>4779</v>
+        <v>86981</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102306</v>
+        <v>6003295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>715317</v>
+        <v>715736</v>
       </c>
       <c r="R39" t="n">
-        <v>6368305</v>
+        <v>6368332</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4521,50 +4521,51 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128721630</v>
+        <v>128721561</v>
       </c>
       <c r="B40" t="n">
-        <v>86978</v>
+        <v>4779</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6003295</v>
+        <v>102306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4574,10 +4575,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>715736</v>
+        <v>715317</v>
       </c>
       <c r="R40" t="n">
-        <v>6368332</v>
+        <v>6368305</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4618,19 +4619,18 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4737,7 +4737,7 @@
         <v>128721498</v>
       </c>
       <c r="B42" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>128721566</v>
       </c>
       <c r="B44" t="n">
-        <v>98658</v>
+        <v>98661</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>128721556</v>
       </c>
       <c r="B45" t="n">
-        <v>87000</v>
+        <v>87003</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>128721551</v>
       </c>
       <c r="B47" t="n">
-        <v>86894</v>
+        <v>86897</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -4734,32 +4734,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128721498</v>
+        <v>128721536</v>
       </c>
       <c r="B42" t="n">
-        <v>87026</v>
+        <v>75155</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3767</v>
+        <v>6426</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>715536</v>
+        <v>715317</v>
       </c>
       <c r="R42" t="n">
-        <v>6368516</v>
+        <v>6368307</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4831,32 +4831,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128721536</v>
+        <v>128721498</v>
       </c>
       <c r="B43" t="n">
-        <v>75155</v>
+        <v>87026</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6426</v>
+        <v>3767</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4866,10 +4866,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>715317</v>
+        <v>715536</v>
       </c>
       <c r="R43" t="n">
-        <v>6368307</v>
+        <v>6368516</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -3858,32 +3858,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128721573</v>
+        <v>128721633</v>
       </c>
       <c r="B33" t="n">
-        <v>86944</v>
+        <v>86981</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>715594</v>
+        <v>715511</v>
       </c>
       <c r="R33" t="n">
-        <v>6368467</v>
+        <v>6368537</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3937,50 +3937,51 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128721633</v>
+        <v>128721573</v>
       </c>
       <c r="B34" t="n">
-        <v>86981</v>
+        <v>86944</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3990,10 +3991,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>715511</v>
+        <v>715594</v>
       </c>
       <c r="R34" t="n">
-        <v>6368537</v>
+        <v>6368467</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4034,19 +4035,18 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4151,32 +4151,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128721555</v>
+        <v>128721565</v>
       </c>
       <c r="B36" t="n">
-        <v>87003</v>
+        <v>98661</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>449</v>
+        <v>219811</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4186,10 +4186,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>715312</v>
+        <v>715699</v>
       </c>
       <c r="R36" t="n">
-        <v>6368391</v>
+        <v>6368412</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4345,32 +4345,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128721565</v>
+        <v>128721555</v>
       </c>
       <c r="B38" t="n">
-        <v>98661</v>
+        <v>87003</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219811</v>
+        <v>449</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715699</v>
+        <v>715312</v>
       </c>
       <c r="R38" t="n">
-        <v>6368412</v>
+        <v>6368391</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -3858,32 +3858,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128721633</v>
+        <v>128721573</v>
       </c>
       <c r="B33" t="n">
-        <v>86981</v>
+        <v>86944</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>715511</v>
+        <v>715594</v>
       </c>
       <c r="R33" t="n">
-        <v>6368537</v>
+        <v>6368467</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3937,51 +3937,50 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128721573</v>
+        <v>128721633</v>
       </c>
       <c r="B34" t="n">
-        <v>86944</v>
+        <v>86981</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3991,10 +3990,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>715594</v>
+        <v>715511</v>
       </c>
       <c r="R34" t="n">
-        <v>6368467</v>
+        <v>6368537</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4035,18 +4034,19 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4151,32 +4151,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128721565</v>
+        <v>128721555</v>
       </c>
       <c r="B36" t="n">
-        <v>98661</v>
+        <v>87003</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219811</v>
+        <v>449</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4186,10 +4186,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>715699</v>
+        <v>715312</v>
       </c>
       <c r="R36" t="n">
-        <v>6368412</v>
+        <v>6368391</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4345,32 +4345,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128721555</v>
+        <v>128721565</v>
       </c>
       <c r="B38" t="n">
-        <v>87003</v>
+        <v>98661</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>449</v>
+        <v>219811</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715312</v>
+        <v>715699</v>
       </c>
       <c r="R38" t="n">
-        <v>6368391</v>
+        <v>6368412</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen, Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4734,32 +4734,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128721536</v>
+        <v>128721498</v>
       </c>
       <c r="B42" t="n">
-        <v>75155</v>
+        <v>87026</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6426</v>
+        <v>3767</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>715317</v>
+        <v>715536</v>
       </c>
       <c r="R42" t="n">
-        <v>6368307</v>
+        <v>6368516</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4831,32 +4831,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128721498</v>
+        <v>128721536</v>
       </c>
       <c r="B43" t="n">
-        <v>87026</v>
+        <v>75155</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3767</v>
+        <v>6426</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4866,10 +4866,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>715536</v>
+        <v>715317</v>
       </c>
       <c r="R43" t="n">
-        <v>6368516</v>
+        <v>6368307</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -3764,7 +3764,7 @@
         <v>128721535</v>
       </c>
       <c r="B32" t="n">
-        <v>75155</v>
+        <v>75157</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>128721573</v>
       </c>
       <c r="B33" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>128721633</v>
       </c>
       <c r="B34" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>128721515</v>
       </c>
       <c r="B35" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4151,32 +4151,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128721555</v>
+        <v>128721565</v>
       </c>
       <c r="B36" t="n">
-        <v>87003</v>
+        <v>98671</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>449</v>
+        <v>219811</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4186,10 +4186,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>715312</v>
+        <v>715699</v>
       </c>
       <c r="R36" t="n">
-        <v>6368391</v>
+        <v>6368412</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4248,32 +4248,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128721574</v>
+        <v>128721555</v>
       </c>
       <c r="B37" t="n">
-        <v>86944</v>
+        <v>87007</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715274</v>
+        <v>715312</v>
       </c>
       <c r="R37" t="n">
-        <v>6368569</v>
+        <v>6368391</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4345,10 +4345,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128721565</v>
+        <v>128721574</v>
       </c>
       <c r="B38" t="n">
-        <v>98661</v>
+        <v>86948</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4356,21 +4356,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219811</v>
+        <v>3674</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715699</v>
+        <v>715274</v>
       </c>
       <c r="R38" t="n">
-        <v>6368412</v>
+        <v>6368569</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4445,7 +4445,7 @@
         <v>128721630</v>
       </c>
       <c r="B39" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>128721532</v>
       </c>
       <c r="B41" t="n">
-        <v>75155</v>
+        <v>75157</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4734,32 +4734,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128721498</v>
+        <v>128721536</v>
       </c>
       <c r="B42" t="n">
-        <v>87026</v>
+        <v>75157</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3767</v>
+        <v>6426</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>715536</v>
+        <v>715317</v>
       </c>
       <c r="R42" t="n">
-        <v>6368516</v>
+        <v>6368307</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4831,32 +4831,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128721536</v>
+        <v>128721498</v>
       </c>
       <c r="B43" t="n">
-        <v>75155</v>
+        <v>87030</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6426</v>
+        <v>3767</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4866,10 +4866,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>715317</v>
+        <v>715536</v>
       </c>
       <c r="R43" t="n">
-        <v>6368307</v>
+        <v>6368516</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4931,7 +4931,7 @@
         <v>128721566</v>
       </c>
       <c r="B44" t="n">
-        <v>98661</v>
+        <v>98671</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>128721556</v>
       </c>
       <c r="B45" t="n">
-        <v>87003</v>
+        <v>87007</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>128721533</v>
       </c>
       <c r="B46" t="n">
-        <v>75155</v>
+        <v>75157</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>128721551</v>
       </c>
       <c r="B47" t="n">
-        <v>86897</v>
+        <v>86901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -4442,32 +4442,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128721630</v>
+        <v>128721561</v>
       </c>
       <c r="B39" t="n">
-        <v>86985</v>
+        <v>4779</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6003295</v>
+        <v>102306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>715736</v>
+        <v>715317</v>
       </c>
       <c r="R39" t="n">
-        <v>6368332</v>
+        <v>6368305</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4521,51 +4521,50 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128721561</v>
+        <v>128721630</v>
       </c>
       <c r="B40" t="n">
-        <v>4779</v>
+        <v>86985</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102306</v>
+        <v>6003295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4575,10 +4574,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>715317</v>
+        <v>715736</v>
       </c>
       <c r="R40" t="n">
-        <v>6368305</v>
+        <v>6368332</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4619,18 +4618,19 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4734,32 +4734,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128721536</v>
+        <v>128721498</v>
       </c>
       <c r="B42" t="n">
-        <v>75157</v>
+        <v>87030</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6426</v>
+        <v>3767</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>715317</v>
+        <v>715536</v>
       </c>
       <c r="R42" t="n">
-        <v>6368307</v>
+        <v>6368516</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4831,32 +4831,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128721498</v>
+        <v>128721536</v>
       </c>
       <c r="B43" t="n">
-        <v>87030</v>
+        <v>75157</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3767</v>
+        <v>6426</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4866,10 +4866,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>715536</v>
+        <v>715317</v>
       </c>
       <c r="R43" t="n">
-        <v>6368516</v>
+        <v>6368307</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -5222,7 +5222,7 @@
         <v>128721551</v>
       </c>
       <c r="B47" t="n">
-        <v>86901</v>
+        <v>86908</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -3764,7 +3764,7 @@
         <v>128721535</v>
       </c>
       <c r="B32" t="n">
-        <v>75157</v>
+        <v>75159</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>128721573</v>
       </c>
       <c r="B33" t="n">
-        <v>86948</v>
+        <v>86957</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>128721633</v>
       </c>
       <c r="B34" t="n">
-        <v>86985</v>
+        <v>86994</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>128721515</v>
       </c>
       <c r="B35" t="n">
-        <v>86985</v>
+        <v>86994</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4151,32 +4151,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128721565</v>
+        <v>128721555</v>
       </c>
       <c r="B36" t="n">
-        <v>98671</v>
+        <v>87016</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219811</v>
+        <v>449</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4186,10 +4186,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>715699</v>
+        <v>715312</v>
       </c>
       <c r="R36" t="n">
-        <v>6368412</v>
+        <v>6368391</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4248,32 +4248,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128721555</v>
+        <v>128721565</v>
       </c>
       <c r="B37" t="n">
-        <v>87007</v>
+        <v>98680</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>449</v>
+        <v>219811</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715312</v>
+        <v>715699</v>
       </c>
       <c r="R37" t="n">
-        <v>6368391</v>
+        <v>6368412</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4348,7 +4348,7 @@
         <v>128721574</v>
       </c>
       <c r="B38" t="n">
-        <v>86948</v>
+        <v>86957</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4442,32 +4442,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128721561</v>
+        <v>128721630</v>
       </c>
       <c r="B39" t="n">
-        <v>4779</v>
+        <v>86994</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102306</v>
+        <v>6003295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>715317</v>
+        <v>715736</v>
       </c>
       <c r="R39" t="n">
-        <v>6368305</v>
+        <v>6368332</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4521,50 +4521,51 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128721630</v>
+        <v>128721561</v>
       </c>
       <c r="B40" t="n">
-        <v>86985</v>
+        <v>4779</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6003295</v>
+        <v>102306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4574,10 +4575,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>715736</v>
+        <v>715317</v>
       </c>
       <c r="R40" t="n">
-        <v>6368332</v>
+        <v>6368305</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4618,19 +4619,18 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4640,7 +4640,7 @@
         <v>128721532</v>
       </c>
       <c r="B41" t="n">
-        <v>75157</v>
+        <v>75159</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>128721498</v>
       </c>
       <c r="B42" t="n">
-        <v>87030</v>
+        <v>87039</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>128721536</v>
       </c>
       <c r="B43" t="n">
-        <v>75157</v>
+        <v>75159</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>128721566</v>
       </c>
       <c r="B44" t="n">
-        <v>98671</v>
+        <v>98680</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>128721556</v>
       </c>
       <c r="B45" t="n">
-        <v>87007</v>
+        <v>87016</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>128721533</v>
       </c>
       <c r="B46" t="n">
-        <v>75157</v>
+        <v>75159</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>128721551</v>
       </c>
       <c r="B47" t="n">
-        <v>86908</v>
+        <v>86910</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -5222,7 +5222,7 @@
         <v>128721551</v>
       </c>
       <c r="B47" t="n">
-        <v>86910</v>
+        <v>86911</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -5319,7 +5319,7 @@
         <v>131299153</v>
       </c>
       <c r="B48" t="n">
-        <v>98701</v>
+        <v>98702</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -5319,7 +5319,7 @@
         <v>131299153</v>
       </c>
       <c r="B48" t="n">
-        <v>98702</v>
+        <v>98704</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -5319,7 +5319,7 @@
         <v>131299153</v>
       </c>
       <c r="B48" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -5319,7 +5319,7 @@
         <v>131299153</v>
       </c>
       <c r="B48" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -5319,7 +5319,7 @@
         <v>131299153</v>
       </c>
       <c r="B48" t="n">
-        <v>98706</v>
+        <v>98709</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -5319,7 +5319,7 @@
         <v>131299153</v>
       </c>
       <c r="B48" t="n">
-        <v>98709</v>
+        <v>98710</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -5319,7 +5319,7 @@
         <v>131299153</v>
       </c>
       <c r="B48" t="n">
-        <v>98710</v>
+        <v>98716</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -5319,7 +5319,7 @@
         <v>131299153</v>
       </c>
       <c r="B48" t="n">
-        <v>98716</v>
+        <v>98717</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -5319,7 +5319,7 @@
         <v>131299153</v>
       </c>
       <c r="B48" t="n">
-        <v>98717</v>
+        <v>98718</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -5319,7 +5319,7 @@
         <v>131299153</v>
       </c>
       <c r="B48" t="n">
-        <v>98718</v>
+        <v>98721</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -5319,7 +5319,7 @@
         <v>131299153</v>
       </c>
       <c r="B48" t="n">
-        <v>98721</v>
+        <v>98727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121366813</v>
+        <v>128721555</v>
       </c>
       <c r="B2" t="n">
-        <v>98098</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219799</v>
+        <v>449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>KÄRR 3150 M VSV ALA K:A_Buttle 9, Gtl</t>
+          <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>715446</v>
+        <v>715312</v>
       </c>
       <c r="R2" t="n">
-        <v>6368460</v>
+        <v>6368391</v>
       </c>
       <c r="S2" t="n">
-        <v>123</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,15 +738,14 @@
           <t>Buttle</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,65 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121364403</v>
+        <v>128721556</v>
       </c>
       <c r="B3" t="n">
-        <v>98786</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222322</v>
+        <v>449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>KÄRR 3450 M SV ALA K:A_Buttle 6, Gtl</t>
+          <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715223</v>
+        <v>715325</v>
       </c>
       <c r="R3" t="n">
-        <v>6368280</v>
+        <v>6368299</v>
       </c>
       <c r="S3" t="n">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -846,15 +835,14 @@
           <t>Buttle</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,65 +857,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121368614</v>
+        <v>121369382</v>
       </c>
       <c r="B4" t="n">
-        <v>99152</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222662</v>
+        <v>1282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Källnate</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Potamogeton coloratus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Hornem.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>KÄRR 3150 M VSV ALA K:A_Buttle 9, Gtl</t>
+          <t>KÄRR 3500 M VSV ALA K:A_Buttle 4, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715446</v>
+        <v>715034</v>
       </c>
       <c r="R4" t="n">
-        <v>6368460</v>
+        <v>6368502</v>
       </c>
       <c r="S4" t="n">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,53 +967,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121367117</v>
+        <v>131299153</v>
       </c>
       <c r="B5" t="n">
-        <v>98044</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98801</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219794</v>
+        <v>1282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sumpnycklar</t>
+          <t>Källnate</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. lapponica</t>
+          <t>Potamogeton coloratus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laest. ex Hartm.) H. Sund.</t>
+          <t>Hornem.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>KÄRR 3150 M VSV ALA K:A_Buttle 9, Gtl</t>
+          <t>Ala, kärr 3,5 km OSO, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715446</v>
+        <v>715034</v>
       </c>
       <c r="R5" t="n">
-        <v>6368460</v>
+        <v>6368501</v>
       </c>
       <c r="S5" t="n">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1052,7 +1030,11 @@
           <t>Buttle</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>I-Got-3922</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
           <t>2023-08-31</t>
@@ -1075,7 +1057,7 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Sofia Lund</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1083,19 +1065,18 @@
           <t>Rikard Anderberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121367247</v>
+        <v>128721573</v>
       </c>
       <c r="B6" t="n">
-        <v>98025</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,37 +1084,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223585</v>
+        <v>3674</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaxnycklar</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. ochroleuca</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Wüstnei ex Boll) Hyl.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>KÄRR 3450 M SV ALA K:A_Buttle 6, Gtl</t>
+          <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715223</v>
+        <v>715594</v>
       </c>
       <c r="R6" t="n">
-        <v>6368280</v>
+        <v>6368467</v>
       </c>
       <c r="S6" t="n">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1155,15 +1136,14 @@
           <t>Buttle</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,27 +1158,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121366018</v>
+        <v>128721574</v>
       </c>
       <c r="B7" t="n">
-        <v>98116</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,33 +1181,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223614</v>
+        <v>3674</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig brudsporre</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. conopsea</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>KÄRR 3150 M VSV ALA K:A_Buttle 9, Gtl</t>
+          <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715446</v>
+        <v>715274</v>
       </c>
       <c r="R7" t="n">
-        <v>6368460</v>
+        <v>6368569</v>
       </c>
       <c r="S7" t="n">
-        <v>123</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1254,15 +1233,14 @@
           <t>Buttle</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,65 +1255,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121364404</v>
+        <v>128721498</v>
       </c>
       <c r="B8" t="n">
-        <v>98786</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87391</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222322</v>
+        <v>3767</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>KÄRR 3500 M VSV ALA K:A_Buttle 4, Gtl</t>
+          <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715034</v>
+        <v>715536</v>
       </c>
       <c r="R8" t="n">
-        <v>6368502</v>
+        <v>6368516</v>
       </c>
       <c r="S8" t="n">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1357,15 +1330,14 @@
           <t>Buttle</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1380,65 +1352,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121364402</v>
+        <v>128721499</v>
       </c>
       <c r="B9" t="n">
-        <v>98786</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87391</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222322</v>
+        <v>3767</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>KÄRR 3300 M VSV ALA K:A_Buttle 7, Gtl</t>
+          <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715218</v>
+        <v>715394</v>
       </c>
       <c r="R9" t="n">
-        <v>6368617</v>
+        <v>6368208</v>
       </c>
       <c r="S9" t="n">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1460,15 +1427,14 @@
           <t>Buttle</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1483,27 +1449,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121369054</v>
+        <v>128721532</v>
       </c>
       <c r="B10" t="n">
-        <v>105117</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,37 +1472,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221137</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>KÄRR 3300 M VSV ALA K:A_Buttle 7, Gtl</t>
+          <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715218</v>
+        <v>715763</v>
       </c>
       <c r="R10" t="n">
-        <v>6368617</v>
+        <v>6368338</v>
       </c>
       <c r="S10" t="n">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1563,15 +1524,14 @@
           <t>Buttle</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1586,65 +1546,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121367376</v>
+        <v>128721533</v>
       </c>
       <c r="B11" t="n">
-        <v>98021</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219788</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>KÄRR 3150 M VSV ALA K:A_Buttle 9, Gtl</t>
+          <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>715446</v>
+        <v>715262</v>
       </c>
       <c r="R11" t="n">
-        <v>6368460</v>
+        <v>6368453</v>
       </c>
       <c r="S11" t="n">
-        <v>123</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1666,15 +1621,14 @@
           <t>Buttle</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1689,65 +1643,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121367246</v>
+        <v>128721535</v>
       </c>
       <c r="B12" t="n">
-        <v>98025</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223585</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaxnycklar</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. ochroleuca</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Wüstnei ex Boll) Hyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>KÄRR 3300 M VSV ALA K:A_Buttle 7, Gtl</t>
+          <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>715218</v>
+        <v>715312</v>
       </c>
       <c r="R12" t="n">
-        <v>6368617</v>
+        <v>6368398</v>
       </c>
       <c r="S12" t="n">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1769,15 +1718,14 @@
           <t>Buttle</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1792,65 +1740,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121369382</v>
+        <v>128721536</v>
       </c>
       <c r="B13" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1282</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Källnate</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Potamogeton coloratus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hornem.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>KÄRR 3500 M VSV ALA K:A_Buttle 4, Gtl</t>
+          <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>715034</v>
+        <v>715317</v>
       </c>
       <c r="R13" t="n">
-        <v>6368502</v>
+        <v>6368307</v>
       </c>
       <c r="S13" t="n">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1872,15 +1815,14 @@
           <t>Buttle</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1895,65 +1837,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121366815</v>
+        <v>121365843</v>
       </c>
       <c r="B14" t="n">
-        <v>98098</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43212</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219799</v>
+        <v>101070</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Silversmygare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Hesperia comma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>KÄRR 3300 M VSV ALA K:A_Buttle 7, Gtl</t>
+          <t>KÄRR 3150 M VSV ALA K:A_Buttle 9, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>715218</v>
+        <v>715446</v>
       </c>
       <c r="R14" t="n">
-        <v>6368617</v>
+        <v>6368460</v>
       </c>
       <c r="S14" t="n">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2010,53 +1947,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121364400</v>
+        <v>128721561</v>
       </c>
       <c r="B15" t="n">
-        <v>98786</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222322</v>
+        <v>102306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>KÄRR 3150 M VSV ALA K:A_Buttle 9, Gtl</t>
+          <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>715446</v>
+        <v>715317</v>
       </c>
       <c r="R15" t="n">
-        <v>6368460</v>
+        <v>6368305</v>
       </c>
       <c r="S15" t="n">
-        <v>123</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2078,15 +2010,14 @@
           <t>Buttle</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2101,27 +2032,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121368617</v>
+        <v>121367376</v>
       </c>
       <c r="B16" t="n">
-        <v>99152</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99026</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,37 +2055,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222662</v>
+        <v>219788</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>KÄRR 3450 M SV ALA K:A_Buttle 6, Gtl</t>
+          <t>KÄRR 3150 M VSV ALA K:A_Buttle 9, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>715223</v>
+        <v>715446</v>
       </c>
       <c r="R16" t="n">
-        <v>6368280</v>
+        <v>6368460</v>
       </c>
       <c r="S16" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2216,15 +2142,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121366818</v>
+        <v>121367378</v>
       </c>
       <c r="B17" t="n">
-        <v>98098</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99026</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2232,37 +2153,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219799</v>
+        <v>219788</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>KÄRR 3500 M VSV ALA K:A_Buttle 4, Gtl</t>
+          <t>KÄRR 3450 M SV ALA K:A_Buttle 6, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>715034</v>
+        <v>715223</v>
       </c>
       <c r="R17" t="n">
-        <v>6368502</v>
+        <v>6368280</v>
       </c>
       <c r="S17" t="n">
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2319,53 +2240,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121368862</v>
+        <v>121367379</v>
       </c>
       <c r="B18" t="n">
-        <v>67269</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99026</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>263680</v>
+        <v>219788</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blodkula</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rivularia haematites</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>C.Agardh ex  Bornet &amp; Flahault</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>KÄRR 3450 M SV ALA K:A_Buttle 6, Gtl</t>
+          <t>KÄRR 3500 M VSV ALA K:A_Buttle 4, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>715223</v>
+        <v>715034</v>
       </c>
       <c r="R18" t="n">
-        <v>6368280</v>
+        <v>6368502</v>
       </c>
       <c r="S18" t="n">
-        <v>121</v>
+        <v>67</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2422,15 +2338,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121368616</v>
+        <v>121367117</v>
       </c>
       <c r="B19" t="n">
-        <v>99152</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99049</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2438,37 +2349,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222662</v>
+        <v>219794</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Sumpnycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>KÄRR 3300 M VSV ALA K:A_Buttle 7, Gtl</t>
+          <t>KÄRR 3150 M VSV ALA K:A_Buttle 9, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>715218</v>
+        <v>715446</v>
       </c>
       <c r="R19" t="n">
-        <v>6368617</v>
+        <v>6368460</v>
       </c>
       <c r="S19" t="n">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2525,15 +2436,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121367379</v>
+        <v>121367118</v>
       </c>
       <c r="B20" t="n">
-        <v>98021</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99049</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2541,37 +2447,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219788</v>
+        <v>219794</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Sumpnycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>KÄRR 3500 M VSV ALA K:A_Buttle 4, Gtl</t>
+          <t>KÄRR 3450 M SV ALA K:A_Buttle 6, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>715034</v>
+        <v>715223</v>
       </c>
       <c r="R20" t="n">
-        <v>6368502</v>
+        <v>6368280</v>
       </c>
       <c r="S20" t="n">
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2628,37 +2534,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121369052</v>
+        <v>121366813</v>
       </c>
       <c r="B21" t="n">
-        <v>105117</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99103</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221137</v>
+        <v>219799</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2731,15 +2632,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121366070</v>
+        <v>121366815</v>
       </c>
       <c r="B22" t="n">
-        <v>98115</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99103</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2747,37 +2643,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219811</v>
+        <v>219799</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>KÄRR 3450 M SV ALA K:A_Buttle 6, Gtl</t>
+          <t>KÄRR 3300 M VSV ALA K:A_Buttle 7, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>715223</v>
+        <v>715218</v>
       </c>
       <c r="R22" t="n">
-        <v>6368280</v>
+        <v>6368617</v>
       </c>
       <c r="S22" t="n">
-        <v>121</v>
+        <v>71</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2834,53 +2730,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121365843</v>
+        <v>121366817</v>
       </c>
       <c r="B23" t="n">
-        <v>42749</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99103</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101070</v>
+        <v>219799</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Silversmygare</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hesperia comma</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>KÄRR 3150 M VSV ALA K:A_Buttle 9, Gtl</t>
+          <t>KÄRR 3450 M SV ALA K:A_Buttle 6, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>715446</v>
+        <v>715223</v>
       </c>
       <c r="R23" t="n">
-        <v>6368460</v>
+        <v>6368280</v>
       </c>
       <c r="S23" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2937,15 +2828,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121368618</v>
+        <v>121366818</v>
       </c>
       <c r="B24" t="n">
-        <v>99152</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99103</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2953,21 +2839,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222662</v>
+        <v>219799</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3040,15 +2926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121367378</v>
+        <v>121366069</v>
       </c>
       <c r="B25" t="n">
-        <v>98021</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3056,37 +2937,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219788</v>
+        <v>219811</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>KÄRR 3450 M SV ALA K:A_Buttle 6, Gtl</t>
+          <t>KÄRR 3300 M VSV ALA K:A_Buttle 7, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>715223</v>
+        <v>715218</v>
       </c>
       <c r="R25" t="n">
-        <v>6368280</v>
+        <v>6368617</v>
       </c>
       <c r="S25" t="n">
-        <v>121</v>
+        <v>71</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3143,37 +3024,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121369055</v>
+        <v>121366070</v>
       </c>
       <c r="B26" t="n">
-        <v>105117</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221137</v>
+        <v>219811</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3246,53 +3122,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121369056</v>
+        <v>128721565</v>
       </c>
       <c r="B27" t="n">
-        <v>105117</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221137</v>
+        <v>219811</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>KÄRR 3500 M VSV ALA K:A_Buttle 4, Gtl</t>
+          <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>715034</v>
+        <v>715699</v>
       </c>
       <c r="R27" t="n">
-        <v>6368502</v>
+        <v>6368412</v>
       </c>
       <c r="S27" t="n">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3314,15 +3185,14 @@
           <t>Buttle</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3337,27 +3207,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121367248</v>
+        <v>128721566</v>
       </c>
       <c r="B28" t="n">
-        <v>98025</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3365,37 +3230,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>223585</v>
+        <v>219811</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vaxnycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. ochroleuca</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Wüstnei ex Boll) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>KÄRR 3500 M VSV ALA K:A_Buttle 4, Gtl</t>
+          <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>715034</v>
+        <v>715339</v>
       </c>
       <c r="R28" t="n">
-        <v>6368502</v>
+        <v>6368362</v>
       </c>
       <c r="S28" t="n">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3417,15 +3282,14 @@
           <t>Buttle</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3440,65 +3304,60 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121367118</v>
+        <v>121369052</v>
       </c>
       <c r="B29" t="n">
-        <v>98044</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106140</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219794</v>
+        <v>221137</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sumpnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. lapponica</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Laest. ex Hartm.) H. Sund.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>KÄRR 3450 M SV ALA K:A_Buttle 6, Gtl</t>
+          <t>KÄRR 3150 M VSV ALA K:A_Buttle 9, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>715223</v>
+        <v>715446</v>
       </c>
       <c r="R29" t="n">
-        <v>6368280</v>
+        <v>6368460</v>
       </c>
       <c r="S29" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3555,37 +3414,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121366069</v>
+        <v>121369054</v>
       </c>
       <c r="B30" t="n">
-        <v>98115</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106140</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219811</v>
+        <v>221137</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3658,37 +3512,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121366817</v>
+        <v>121369055</v>
       </c>
       <c r="B31" t="n">
-        <v>98098</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106140</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219799</v>
+        <v>221137</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3761,48 +3610,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128721535</v>
+        <v>121369056</v>
       </c>
       <c r="B32" t="n">
-        <v>75159</v>
+        <v>106140</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6426</v>
+        <v>221137</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gyle, Gtl</t>
+          <t>KÄRR 3500 M VSV ALA K:A_Buttle 4, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>715312</v>
+        <v>715034</v>
       </c>
       <c r="R32" t="n">
-        <v>6368398</v>
+        <v>6368502</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3824,14 +3673,15 @@
           <t>Buttle</t>
         </is>
       </c>
+      <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3846,44 +3696,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128721573</v>
+        <v>128721648</v>
       </c>
       <c r="B33" t="n">
-        <v>86957</v>
+        <v>107516</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3674</v>
+        <v>221849</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3893,10 +3743,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>715594</v>
+        <v>715772</v>
       </c>
       <c r="R33" t="n">
-        <v>6368467</v>
+        <v>6368230</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3943,22 +3793,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128721633</v>
+        <v>121364400</v>
       </c>
       <c r="B34" t="n">
-        <v>86994</v>
+        <v>99803</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3966,37 +3816,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6003295</v>
+        <v>222322</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gyle, Gtl</t>
+          <t>KÄRR 3150 M VSV ALA K:A_Buttle 9, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>715511</v>
+        <v>715446</v>
       </c>
       <c r="R34" t="n">
-        <v>6368537</v>
+        <v>6368460</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4018,14 +3868,15 @@
           <t>Buttle</t>
         </is>
       </c>
+      <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4034,29 +3885,28 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128721515</v>
+        <v>121364402</v>
       </c>
       <c r="B35" t="n">
-        <v>86994</v>
+        <v>99803</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4064,37 +3914,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6003295</v>
+        <v>222322</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gyle, Gtl</t>
+          <t>KÄRR 3300 M VSV ALA K:A_Buttle 7, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>715687</v>
+        <v>715218</v>
       </c>
       <c r="R35" t="n">
-        <v>6368449</v>
+        <v>6368617</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4116,14 +3966,15 @@
           <t>Buttle</t>
         </is>
       </c>
+      <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4132,67 +3983,66 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128721555</v>
+        <v>121364403</v>
       </c>
       <c r="B36" t="n">
-        <v>87016</v>
+        <v>99803</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>449</v>
+        <v>222322</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gyle, Gtl</t>
+          <t>KÄRR 3450 M SV ALA K:A_Buttle 6, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>715312</v>
+        <v>715223</v>
       </c>
       <c r="R36" t="n">
-        <v>6368391</v>
+        <v>6368280</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>121</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4214,14 +4064,15 @@
           <t>Buttle</t>
         </is>
       </c>
+      <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4236,60 +4087,60 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128721565</v>
+        <v>121364404</v>
       </c>
       <c r="B37" t="n">
-        <v>98680</v>
+        <v>99803</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219811</v>
+        <v>222322</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gyle, Gtl</t>
+          <t>KÄRR 3500 M VSV ALA K:A_Buttle 4, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715699</v>
+        <v>715034</v>
       </c>
       <c r="R37" t="n">
-        <v>6368412</v>
+        <v>6368502</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4311,14 +4162,15 @@
           <t>Buttle</t>
         </is>
       </c>
+      <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4333,22 +4185,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128721574</v>
+        <v>121368614</v>
       </c>
       <c r="B38" t="n">
-        <v>86957</v>
+        <v>100171</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4356,37 +4208,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3674</v>
+        <v>222662</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gyle, Gtl</t>
+          <t>KÄRR 3150 M VSV ALA K:A_Buttle 9, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715274</v>
+        <v>715446</v>
       </c>
       <c r="R38" t="n">
-        <v>6368569</v>
+        <v>6368460</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4408,14 +4260,15 @@
           <t>Buttle</t>
         </is>
       </c>
+      <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4430,60 +4283,60 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128721630</v>
+        <v>121368616</v>
       </c>
       <c r="B39" t="n">
-        <v>86994</v>
+        <v>100171</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6003295</v>
+        <v>222662</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gyle, Gtl</t>
+          <t>KÄRR 3300 M VSV ALA K:A_Buttle 7, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>715736</v>
+        <v>715218</v>
       </c>
       <c r="R39" t="n">
-        <v>6368332</v>
+        <v>6368617</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4505,14 +4358,15 @@
           <t>Buttle</t>
         </is>
       </c>
+      <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4521,29 +4375,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128721561</v>
+        <v>121368617</v>
       </c>
       <c r="B40" t="n">
-        <v>4779</v>
+        <v>100171</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4551,37 +4404,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102306</v>
+        <v>222662</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gyle, Gtl</t>
+          <t>KÄRR 3450 M SV ALA K:A_Buttle 6, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>715317</v>
+        <v>715223</v>
       </c>
       <c r="R40" t="n">
-        <v>6368305</v>
+        <v>6368280</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>121</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4603,14 +4456,15 @@
           <t>Buttle</t>
         </is>
       </c>
+      <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4625,22 +4479,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128721532</v>
+        <v>121368618</v>
       </c>
       <c r="B41" t="n">
-        <v>75159</v>
+        <v>100171</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4648,37 +4502,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6426</v>
+        <v>222662</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gyle, Gtl</t>
+          <t>KÄRR 3500 M VSV ALA K:A_Buttle 4, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>715763</v>
+        <v>715034</v>
       </c>
       <c r="R41" t="n">
-        <v>6368338</v>
+        <v>6368502</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4700,14 +4554,15 @@
           <t>Buttle</t>
         </is>
       </c>
+      <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4722,60 +4577,60 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128721498</v>
+        <v>121367246</v>
       </c>
       <c r="B42" t="n">
-        <v>87039</v>
+        <v>99030</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3767</v>
+        <v>223585</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Vaxnycklar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Dactylorhiza incarnata var. ochroleuca</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Wüstnei ex Boll) Hyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gyle, Gtl</t>
+          <t>KÄRR 3300 M VSV ALA K:A_Buttle 7, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>715536</v>
+        <v>715218</v>
       </c>
       <c r="R42" t="n">
-        <v>6368516</v>
+        <v>6368617</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4797,14 +4652,15 @@
           <t>Buttle</t>
         </is>
       </c>
+      <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4819,22 +4675,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128721536</v>
+        <v>121367247</v>
       </c>
       <c r="B43" t="n">
-        <v>75159</v>
+        <v>99030</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4842,37 +4698,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6426</v>
+        <v>223585</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vaxnycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dactylorhiza incarnata var. ochroleuca</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Wüstnei ex Boll) Hyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gyle, Gtl</t>
+          <t>KÄRR 3450 M SV ALA K:A_Buttle 6, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>715317</v>
+        <v>715223</v>
       </c>
       <c r="R43" t="n">
-        <v>6368307</v>
+        <v>6368280</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>121</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4894,14 +4750,15 @@
           <t>Buttle</t>
         </is>
       </c>
+      <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4916,22 +4773,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128721566</v>
+        <v>121367248</v>
       </c>
       <c r="B44" t="n">
-        <v>98680</v>
+        <v>99030</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4939,37 +4796,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219811</v>
+        <v>223585</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Vaxnycklar</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza incarnata var. ochroleuca</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wüstnei ex Boll) Hyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gyle, Gtl</t>
+          <t>KÄRR 3500 M VSV ALA K:A_Buttle 4, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>715339</v>
+        <v>715034</v>
       </c>
       <c r="R44" t="n">
-        <v>6368362</v>
+        <v>6368502</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4991,14 +4848,15 @@
           <t>Buttle</t>
         </is>
       </c>
+      <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5013,60 +4871,56 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128721556</v>
+        <v>121366018</v>
       </c>
       <c r="B45" t="n">
-        <v>87016</v>
+        <v>99121</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>449</v>
+        <v>223614</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Vanlig brudsporre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kytöv. &amp; al.</t>
-        </is>
-      </c>
+          <t>Gymnadenia conopsea subsp. conopsea</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gyle, Gtl</t>
+          <t>KÄRR 3150 M VSV ALA K:A_Buttle 9, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>715325</v>
+        <v>715446</v>
       </c>
       <c r="R45" t="n">
-        <v>6368299</v>
+        <v>6368460</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5088,14 +4942,15 @@
           <t>Buttle</t>
         </is>
       </c>
+      <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5110,44 +4965,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128721533</v>
+        <v>128721551</v>
       </c>
       <c r="B46" t="n">
-        <v>75159</v>
+        <v>87262</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6426</v>
+        <v>248956</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5157,10 +5012,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>715262</v>
+        <v>715379</v>
       </c>
       <c r="R46" t="n">
-        <v>6368453</v>
+        <v>6368253</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5219,48 +5074,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128721551</v>
+        <v>121368862</v>
       </c>
       <c r="B47" t="n">
-        <v>86911</v>
+        <v>67991</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>248956</v>
+        <v>263680</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blodkula</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Rivularia haematites</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>C.Agardh ex  Bornet &amp; Flahault</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Gyle, Gtl</t>
+          <t>KÄRR 3450 M SV ALA K:A_Buttle 6, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>715379</v>
+        <v>715223</v>
       </c>
       <c r="R47" t="n">
-        <v>6368253</v>
+        <v>6368280</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>121</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5282,14 +5137,15 @@
           <t>Buttle</t>
         </is>
       </c>
+      <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5304,60 +5160,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131299153</v>
+        <v>128721515</v>
       </c>
       <c r="B48" t="n">
-        <v>98727</v>
+        <v>87346</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1282</v>
+        <v>6003295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Källnate</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Potamogeton coloratus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Hornem.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Ala, kärr 3,5 km OSO, Gtl</t>
+          <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>715034</v>
+        <v>715687</v>
       </c>
       <c r="R48" t="n">
-        <v>6368501</v>
+        <v>6368449</v>
       </c>
       <c r="S48" t="n">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5379,19 +5235,14 @@
           <t>Buttle</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>I-Got-3922</t>
-        </is>
-      </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5400,25 +5251,218 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Sofia Lund</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128721630</v>
+      </c>
+      <c r="B49" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Gyle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>715736</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6368332</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128721633</v>
+      </c>
+      <c r="B50" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Gyle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>715511</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6368537</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15068-2025 artfynd.xlsx
+++ b/artfynd/A 15068-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721555</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721556</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121369382</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131299153</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721573</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721574</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721498</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721499</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721532</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721533</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1749,6 +1804,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721535</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1846,6 +1906,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721536</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1944,6 +2009,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121365843</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2041,6 +2111,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721561</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2139,6 +2214,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121367376</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2237,6 +2317,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121367378</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2335,6 +2420,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121367379</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2433,6 +2523,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121367117</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2531,6 +2626,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121367118</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2629,6 +2729,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121366813</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2727,6 +2832,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121366815</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2825,6 +2935,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121366817</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2923,6 +3038,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121366818</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3021,6 +3141,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121366069</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3119,6 +3244,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121366070</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3216,6 +3346,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721565</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3313,6 +3448,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721566</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3411,6 +3551,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121369052</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3509,6 +3654,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121369054</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3607,6 +3757,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121369055</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3705,6 +3860,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121369056</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3802,6 +3962,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721648</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3900,6 +4065,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121364400</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3998,6 +4168,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121364402</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4096,6 +4271,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121364403</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4194,6 +4374,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121364404</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4292,6 +4477,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121368614</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4390,6 +4580,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121368616</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4488,6 +4683,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121368617</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4586,6 +4786,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121368618</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4684,6 +4889,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121367246</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4782,6 +4992,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121367247</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4880,6 +5095,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121367248</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4974,6 +5194,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121366018</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5071,6 +5296,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721551</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5169,6 +5399,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121368862</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5267,6 +5502,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721515</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5365,6 +5605,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721630</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5463,8 +5708,64 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721633</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>